--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="帝滙豪庭 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,7 +482,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>帝滙豪庭 - 一手销控汇总明细</t>
+          <t>帝汇豪庭 - 一手销控汇总明细</t>
         </is>
       </c>
     </row>
@@ -677,7 +541,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -727,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -777,7 +641,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -827,7 +691,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -877,7 +741,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -905,7 +769,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -923,7 +787,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -973,7 +837,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1023,7 +887,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1073,7 +937,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1123,7 +987,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1173,7 +1037,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1223,7 +1087,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1273,7 +1137,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1323,7 +1187,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1373,7 +1237,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1423,7 +1287,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1473,7 +1337,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1501,7 +1365,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1519,7 +1383,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1547,7 +1411,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1565,7 +1429,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1615,7 +1479,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1665,7 +1529,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1693,7 +1557,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1711,7 +1575,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1739,7 +1603,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1757,7 +1621,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1807,7 +1671,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1835,7 +1699,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-14</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1853,7 +1717,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1903,7 +1767,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1931,7 +1795,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1949,7 +1813,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1999,7 +1863,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2027,7 +1891,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-10</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2045,7 +1909,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2095,7 +1959,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2123,7 +1987,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2141,7 +2005,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2169,7 +2033,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-07-12</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2187,7 +2051,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2215,7 +2079,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2233,7 +2097,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2261,7 +2125,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2279,7 +2143,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2307,7 +2171,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2325,7 +2189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2375,7 +2239,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2403,7 +2267,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2421,7 +2285,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2471,7 +2335,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2521,7 +2385,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2571,7 +2435,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2621,7 +2485,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2671,7 +2535,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2721,7 +2585,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2771,7 +2635,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2821,7 +2685,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2871,7 +2735,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2921,7 +2785,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2971,7 +2835,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3021,7 +2885,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3049,7 +2913,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3067,7 +2931,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3095,7 +2959,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3113,7 +2977,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3163,7 +3027,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3191,7 +3055,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3209,7 +3073,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3237,7 +3101,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3255,7 +3119,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3283,7 +3147,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3301,7 +3165,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3351,7 +3215,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3379,7 +3243,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3397,7 +3261,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3425,7 +3289,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3443,7 +3307,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3471,7 +3335,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3489,7 +3353,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3539,7 +3403,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3567,7 +3431,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3585,7 +3449,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3613,7 +3477,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3631,7 +3495,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3659,7 +3523,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3677,7 +3541,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3727,7 +3591,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3777,7 +3641,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3805,7 +3669,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3823,7 +3687,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3873,7 +3737,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3923,7 +3787,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3973,7 +3837,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4023,7 +3887,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4051,7 +3915,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4069,7 +3933,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4119,7 +3983,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4147,7 +4011,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4165,7 +4029,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4193,7 +4057,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4211,7 +4075,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4239,7 +4103,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4257,7 +4121,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4307,7 +4171,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4353,7 +4217,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4381,7 +4245,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-24</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4399,7 +4263,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4427,7 +4291,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-04-27</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4445,7 +4309,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4495,7 +4359,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4545,7 +4409,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4573,7 +4437,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4591,7 +4455,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4641,7 +4505,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4669,7 +4533,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4687,7 +4551,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4715,7 +4579,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-03-17</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4733,7 +4597,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4783,7 +4647,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4811,7 +4675,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4829,7 +4693,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4857,7 +4721,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4875,7 +4739,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4903,7 +4767,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-02-21</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4921,7 +4785,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4971,7 +4835,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>帝滙豪庭</t>
+          <t>帝汇豪庭</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -5025,1021 +4889,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>帝滙豪庭 - 帝滙豪庭 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>90 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>39 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>42 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31&amp;32/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 4754呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 4686呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2718呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 2674呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2718呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 2674呎 (3房)
-$15,700万
-$58,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$6,950万
-$40,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$4,180万
-$40,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$6,680万
-$38,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$3,990万
-$38,962/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$6,520万
-$37,579/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$3,042万
-$25,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$6,519万
-$37,572/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,988万
-$25,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$6,350万
-$36,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-$2,660万
-$26,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,995万
-$25,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-$4,000万
-$23,500/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,971万
-$25,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$6,000万
-$34,582/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-$2,568万
-$25,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$5,850万
-$33,718/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-$2,486万
-$24,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,720万
-$23,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$3,990万
-$23,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$3,322万
-$32,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,841万
-$24,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$3,933万
-$22,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$3,241万
-$31,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,724万
-$23,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$3,190万
-$31,155/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$5,280万
-$30,432/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$5,148万
-$29,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$2,435万
-$23,776/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,688万
-$22,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$3,904万
-$22,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 1023呎 (2房)
-$2,424万
-$23,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,650万
-$22,473/呎
-(16年-01月)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-$3,038万
-$29,671/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 1735呎 (4+房)
-$4,945万
-$28,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1024呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 1179呎 (3房)
-$2,720万
-$23,070/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 1702呎 (4+房)
-$3,642万
-$21,400/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1670呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 978呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 1129呎 (3房)
-$3,048万
-$27,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 1639呎 (4+房)
-$4,105万
-$25,047/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="帝汇豪庭" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4889,4 +5068,1021 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>帝汇豪庭 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31&amp;32</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 4754呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 4686呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2718呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2674呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2718呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 2674呎 (3房)
+$15700万
+$58,714/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$6950万
+$40,058/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$4180万
+$40,820/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$6680万
+$38,500/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$3990万
+$38,962/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$6520万
+$37,579/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$3042万
+$25,800/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$6519万
+$37,572/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2988万
+$25,344/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$6350万
+$36,600/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+$2660万
+$26,000/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2995万
+$25,400/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+$4000万
+$23,500/呎
+(16年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2971万
+$25,200/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$6000万
+$34,582/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+$2568万
+$25,100/呎
+(16年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$5850万
+$33,718/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+$2486万
+$24,300/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2720万
+$23,067/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$3990万
+$23,000/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$3322万
+$32,440/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2841万
+$24,100/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$3933万
+$22,671/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$3241万
+$31,649/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2724万
+$23,100/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$3190万
+$31,155/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$5280万
+$30,432/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$5148万
+$29,671/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$2435万
+$23,776/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2688万
+$22,800/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$3904万
+$22,500/呎
+(16年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 1023呎 (2房)
+$2424万
+$23,700/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2650万
+$22,473/呎
+(16年-01月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+$3038万
+$29,671/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 1735呎 (4+房)
+$4945万
+$28,500/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1024呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 1179呎 (3房)
+$2720万
+$23,070/呎
+(16年-03月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 1702呎 (4+房)
+$3642万
+$21,400/呎
+(16年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1670呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 978呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 1129呎 (3房)
+$3048万
+$27,000/呎
+(16年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 1639呎 (4+房)
+$4105万
+$25,047/呎
+(16年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -959,6 +1063,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>58714</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1009,6 +1129,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1059,6 +1199,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1109,6 +1269,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1159,6 +1339,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1209,6 +1409,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1259,6 +1479,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1309,6 +1549,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1359,6 +1619,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1409,6 +1689,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1459,6 +1759,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1509,6 +1829,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1555,6 +1895,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>41800000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>40820</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1601,6 +1957,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>69500000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>40058</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1651,6 +2023,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1701,6 +2093,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1747,6 +2159,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>39897000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>38962</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1793,6 +2221,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>66797500</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>38500</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1843,6 +2287,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1889,6 +2353,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>30418200</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>25800</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1939,6 +2419,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1985,6 +2485,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>65200000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>37579</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2035,6 +2551,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2081,6 +2617,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>29880180</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>25344</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2131,6 +2683,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2177,6 +2749,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>65187000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>37572</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2223,6 +2811,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>39997000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>23500</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2269,6 +2873,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>29947000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>25400</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2315,6 +2935,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>26598000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>26000</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2361,6 +2997,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>63501000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>36600</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2411,6 +3063,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2457,6 +3129,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>29711000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>25200</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2507,6 +3195,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2557,6 +3265,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2607,6 +3335,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2657,6 +3405,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2707,6 +3475,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2757,6 +3545,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2807,6 +3615,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2857,6 +3685,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2907,6 +3755,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2957,6 +3825,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3007,6 +3895,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3057,6 +3965,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3103,6 +4031,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>25677000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>25100</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3149,6 +4093,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>34582</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3199,6 +4159,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3245,6 +4225,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>27196290</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>23067</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3291,6 +4287,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>24859000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>24300</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3337,6 +4349,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>58500000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>33718</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3387,6 +4415,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3433,6 +4481,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>28414000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>24100</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3479,6 +4543,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>33218800</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>32440</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3525,6 +4605,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>39905000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3575,6 +4671,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3621,6 +4737,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>27235000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>23100</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3667,6 +4799,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>32408600</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>31649</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3713,6 +4861,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>39334680</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>22671</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3763,6 +4927,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3813,6 +4997,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3859,6 +5063,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>31902700</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>31155</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3909,6 +5129,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3959,6 +5199,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4009,6 +5269,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4059,6 +5339,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4105,6 +5405,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>52800000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>30432</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4155,6 +5471,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4201,6 +5537,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>26881000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>22800</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4247,6 +5599,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>24347000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>23776</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4293,6 +5661,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>51480000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>29671</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4343,6 +5727,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4389,6 +5793,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>26495370</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>22473</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4435,6 +5855,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>24245000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>23700</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4481,6 +5917,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>39038000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>22500</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4531,6 +5983,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4581,6 +6053,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4627,6 +6119,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>30383100</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>29671</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4677,6 +6185,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4723,6 +6251,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>36423000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>21400</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4769,6 +6313,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>27200000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>23070</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4819,6 +6379,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4865,6 +6445,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>49447500</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>28500</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4911,6 +6507,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>41052330</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>25047</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4957,6 +6569,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>30483000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5007,6 +6635,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5057,13 +6705,33 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5253,7 +6921,7 @@
           <t>B | 2674呎 (3房)
 $15700万
 $58,714/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -5348,7 +7016,7 @@
           <t>A | 1735呎 (4+房)
 $6950万
 $40,058/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -5356,7 +7024,7 @@
           <t>B | 1024呎 (2房)
 $4180万
 $40,820/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -5387,7 +7055,7 @@
           <t>A | 1735呎 (4+房)
 $6680万
 $38,500/呎
-(22年-10月)</t>
+(22年-10月-26日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -5395,7 +7063,7 @@
           <t>B | 1024呎 (2房)
 $3990万
 $38,962/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -5426,7 +7094,7 @@
           <t>A | 1735呎 (4+房)
 $6520万
 $37,579/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -5442,7 +7110,7 @@
           <t>C | 1179呎 (3房)
 $3042万
 $25,800/呎
-(16年-06月)</t>
+(16年-06月-14日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -5465,7 +7133,7 @@
           <t>A | 1735呎 (4+房)
 $6519万
 $37,572/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -5481,7 +7149,7 @@
           <t>C | 1179呎 (3房)
 $2988万
 $25,344/呎
-(16年-04月)</t>
+(16年-04月-10日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5504,7 +7172,7 @@
           <t>A | 1735呎 (4+房)
 $6350万
 $36,600/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5512,7 +7180,7 @@
           <t>B | 1023呎 (2房)
 $2660万
 $26,000/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5520,7 +7188,7 @@
           <t>C | 1179呎 (3房)
 $2995万
 $25,400/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -5528,7 +7196,7 @@
           <t>D | 1702呎 (4+房)
 $4000万
 $23,500/呎
-(16年-07月)</t>
+(16年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -5559,7 +7227,7 @@
           <t>C | 1179呎 (3房)
 $2971万
 $25,200/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -5660,7 +7328,7 @@
           <t>A | 1735呎 (4+房)
 $6000万
 $34,582/呎
-(23年-05月)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5668,7 +7336,7 @@
           <t>B | 1023呎 (2房)
 $2568万
 $25,100/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -5699,7 +7367,7 @@
           <t>A | 1735呎 (4+房)
 $5850万
 $33,718/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5707,7 +7375,7 @@
           <t>B | 1023呎 (2房)
 $2486万
 $24,300/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5715,7 +7383,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,067/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -5738,7 +7406,7 @@
           <t>A | 1735呎 (4+房)
 $3990万
 $23,000/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5746,7 +7414,7 @@
           <t>B | 1024呎 (2房)
 $3322万
 $32,440/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5754,7 +7422,7 @@
           <t>C | 1179呎 (3房)
 $2841万
 $24,100/呎
-(16年-03月)</t>
+(16年-03月-01日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -5777,7 +7445,7 @@
           <t>A | 1735呎 (4+房)
 $3933万
 $22,671/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -5785,7 +7453,7 @@
           <t>B | 1024呎 (2房)
 $3241万
 $31,649/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5793,7 +7461,7 @@
           <t>C | 1179呎 (3房)
 $2724万
 $23,100/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -5824,7 +7492,7 @@
           <t>B | 1024呎 (2房)
 $3190万
 $31,155/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -5855,7 +7523,7 @@
           <t>A | 1735呎 (4+房)
 $5280万
 $30,432/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -5894,7 +7562,7 @@
           <t>A | 1735呎 (4+房)
 $5148万
 $29,671/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -5902,7 +7570,7 @@
           <t>B | 1024呎 (2房)
 $2435万
 $23,776/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -5910,7 +7578,7 @@
           <t>C | 1179呎 (3房)
 $2688万
 $22,800/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -5933,7 +7601,7 @@
           <t>A | 1735呎 (4+房)
 $3904万
 $22,500/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -5941,7 +7609,7 @@
           <t>B | 1023呎 (2房)
 $2424万
 $23,700/呎
-(16年-02月)</t>
+(16年-02月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -5949,7 +7617,7 @@
           <t>C | 1179呎 (3房)
 $2650万
 $22,473/呎
-(16年-01月)</t>
+(16年-01月-23日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -5980,7 +7648,7 @@
           <t>B | 1024呎 (2房)
 $3038万
 $29,671/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -6011,7 +7679,7 @@
           <t>A | 1735呎 (4+房)
 $4945万
 $28,500/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -6027,7 +7695,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,070/呎
-(16年-03月)</t>
+(16年-03月-17日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -6035,7 +7703,7 @@
           <t>D | 1702呎 (4+房)
 $3642万
 $21,400/呎
-(16年-06月)</t>
+(16年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -6066,7 +7734,7 @@
           <t>C | 1129呎 (3房)
 $3048万
 $27,000/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -6074,7 +7742,7 @@
           <t>D | 1639呎 (4+房)
 $4105万
 $25,047/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -6921,7 +6921,7 @@
           <t>B | 2674呎 (3房)
 $15700万
 $58,714/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
           <t>A | 1735呎 (4+房)
 $6950万
 $40,058/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7024,7 +7024,7 @@
           <t>B | 1024呎 (2房)
 $4180万
 $40,820/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -7055,7 +7055,7 @@
           <t>A | 1735呎 (4+房)
 $6680万
 $38,500/呎
-(22年-10月-26日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7063,7 +7063,7 @@
           <t>B | 1024呎 (2房)
 $3990万
 $38,962/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7094,7 +7094,7 @@
           <t>A | 1735呎 (4+房)
 $6520万
 $37,579/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7110,7 +7110,7 @@
           <t>C | 1179呎 (3房)
 $3042万
 $25,800/呎
-(16年-06月-14日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7133,7 +7133,7 @@
           <t>A | 1735呎 (4+房)
 $6519万
 $37,572/呎
-(25年-03月-05日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7149,7 +7149,7 @@
           <t>C | 1179呎 (3房)
 $2988万
 $25,344/呎
-(16年-04月-10日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7172,7 +7172,7 @@
           <t>A | 1735呎 (4+房)
 $6350万
 $36,600/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7180,7 +7180,7 @@
           <t>B | 1023呎 (2房)
 $2660万
 $26,000/呎
-(16年-06月-05日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7188,7 +7188,7 @@
           <t>C | 1179呎 (3房)
 $2995万
 $25,400/呎
-(16年-06月-05日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -7196,7 +7196,7 @@
           <t>D | 1702呎 (4+房)
 $4000万
 $23,500/呎
-(16年-07月-12日)</t>
+(16年-07月)</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
           <t>C | 1179呎 (3房)
 $2971万
 $25,200/呎
-(16年-06月-05日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
           <t>A | 1735呎 (4+房)
 $6000万
 $34,582/呎
-(23年-05月-22日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7336,7 +7336,7 @@
           <t>B | 1023呎 (2房)
 $2568万
 $25,100/呎
-(16年-06月-05日)</t>
+(16年-06月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7367,7 +7367,7 @@
           <t>A | 1735呎 (4+房)
 $5850万
 $33,718/呎
-(24年-07月-07日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7375,7 +7375,7 @@
           <t>B | 1023呎 (2房)
 $2486万
 $24,300/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7383,7 +7383,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,067/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7406,7 +7406,7 @@
           <t>A | 1735呎 (4+房)
 $3990万
 $23,000/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7414,7 +7414,7 @@
           <t>B | 1024呎 (2房)
 $3322万
 $32,440/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7422,7 +7422,7 @@
           <t>C | 1179呎 (3房)
 $2841万
 $24,100/呎
-(16年-03月-01日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -7445,7 +7445,7 @@
           <t>A | 1735呎 (4+房)
 $3933万
 $22,671/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7453,7 +7453,7 @@
           <t>B | 1024呎 (2房)
 $3241万
 $31,649/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7461,7 +7461,7 @@
           <t>C | 1179呎 (3房)
 $2724万
 $23,100/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7492,7 +7492,7 @@
           <t>B | 1024呎 (2房)
 $3190万
 $31,155/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7523,7 +7523,7 @@
           <t>A | 1735呎 (4+房)
 $5280万
 $30,432/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -7562,7 +7562,7 @@
           <t>A | 1735呎 (4+房)
 $5148万
 $29,671/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7570,7 +7570,7 @@
           <t>B | 1024呎 (2房)
 $2435万
 $23,776/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -7578,7 +7578,7 @@
           <t>C | 1179呎 (3房)
 $2688万
 $22,800/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -7601,7 +7601,7 @@
           <t>A | 1735呎 (4+房)
 $3904万
 $22,500/呎
-(16年-04月-27日)</t>
+(16年-04月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7609,7 +7609,7 @@
           <t>B | 1023呎 (2房)
 $2424万
 $23,700/呎
-(16年-02月-24日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -7617,7 +7617,7 @@
           <t>C | 1179呎 (3房)
 $2650万
 $22,473/呎
-(16年-01月-23日)</t>
+(16年-01月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -7648,7 +7648,7 @@
           <t>B | 1024呎 (2房)
 $3038万
 $29,671/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7679,7 +7679,7 @@
           <t>A | 1735呎 (4+房)
 $4945万
 $28,500/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -7695,7 +7695,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,070/呎
-(16年-03月-17日)</t>
+(16年-03月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -7703,7 +7703,7 @@
           <t>D | 1702呎 (4+房)
 $3642万
 $21,400/呎
-(16年-06月-19日)</t>
+(16年-06月)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
           <t>C | 1129呎 (3房)
 $3048万
 $27,000/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -7742,7 +7742,7 @@
           <t>D | 1639呎 (4+房)
 $4105万
 $25,047/呎
-(16年-02月-21日)</t>
+(16年-02月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -6921,7 +6921,7 @@
           <t>B | 2674呎 (3房)
 $15700万
 $58,714/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
           <t>A | 1735呎 (4+房)
 $6950万
 $40,058/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7024,7 +7024,7 @@
           <t>B | 1024呎 (2房)
 $4180万
 $40,820/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -7055,7 +7055,7 @@
           <t>A | 1735呎 (4+房)
 $6680万
 $38,500/呎
-(22年-10月)</t>
+(22年-10月-26日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7063,7 +7063,7 @@
           <t>B | 1024呎 (2房)
 $3990万
 $38,962/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7094,7 +7094,7 @@
           <t>A | 1735呎 (4+房)
 $6520万
 $37,579/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7110,7 +7110,7 @@
           <t>C | 1179呎 (3房)
 $3042万
 $25,800/呎
-(16年-06月)</t>
+(16年-06月-14日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7133,7 +7133,7 @@
           <t>A | 1735呎 (4+房)
 $6519万
 $37,572/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7149,7 +7149,7 @@
           <t>C | 1179呎 (3房)
 $2988万
 $25,344/呎
-(16年-04月)</t>
+(16年-04月-10日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7172,7 +7172,7 @@
           <t>A | 1735呎 (4+房)
 $6350万
 $36,600/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7180,7 +7180,7 @@
           <t>B | 1023呎 (2房)
 $2660万
 $26,000/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7188,7 +7188,7 @@
           <t>C | 1179呎 (3房)
 $2995万
 $25,400/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -7196,7 +7196,7 @@
           <t>D | 1702呎 (4+房)
 $4000万
 $23,500/呎
-(16年-07月)</t>
+(16年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
           <t>C | 1179呎 (3房)
 $2971万
 $25,200/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
           <t>A | 1735呎 (4+房)
 $6000万
 $34,582/呎
-(23年-05月)</t>
+(23年-05月-22日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7336,7 +7336,7 @@
           <t>B | 1023呎 (2房)
 $2568万
 $25,100/呎
-(16年-06月)</t>
+(16年-06月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7367,7 +7367,7 @@
           <t>A | 1735呎 (4+房)
 $5850万
 $33,718/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7375,7 +7375,7 @@
           <t>B | 1023呎 (2房)
 $2486万
 $24,300/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7383,7 +7383,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,067/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7406,7 +7406,7 @@
           <t>A | 1735呎 (4+房)
 $3990万
 $23,000/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7414,7 +7414,7 @@
           <t>B | 1024呎 (2房)
 $3322万
 $32,440/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7422,7 +7422,7 @@
           <t>C | 1179呎 (3房)
 $2841万
 $24,100/呎
-(16年-03月)</t>
+(16年-03月-01日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -7445,7 +7445,7 @@
           <t>A | 1735呎 (4+房)
 $3933万
 $22,671/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7453,7 +7453,7 @@
           <t>B | 1024呎 (2房)
 $3241万
 $31,649/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7461,7 +7461,7 @@
           <t>C | 1179呎 (3房)
 $2724万
 $23,100/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7492,7 +7492,7 @@
           <t>B | 1024呎 (2房)
 $3190万
 $31,155/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7523,7 +7523,7 @@
           <t>A | 1735呎 (4+房)
 $5280万
 $30,432/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -7562,7 +7562,7 @@
           <t>A | 1735呎 (4+房)
 $5148万
 $29,671/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7570,7 +7570,7 @@
           <t>B | 1024呎 (2房)
 $2435万
 $23,776/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -7578,7 +7578,7 @@
           <t>C | 1179呎 (3房)
 $2688万
 $22,800/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -7601,7 +7601,7 @@
           <t>A | 1735呎 (4+房)
 $3904万
 $22,500/呎
-(16年-04月)</t>
+(16年-04月-27日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7609,7 +7609,7 @@
           <t>B | 1023呎 (2房)
 $2424万
 $23,700/呎
-(16年-02月)</t>
+(16年-02月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -7617,7 +7617,7 @@
           <t>C | 1179呎 (3房)
 $2650万
 $22,473/呎
-(16年-01月)</t>
+(16年-01月-23日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -7648,7 +7648,7 @@
           <t>B | 1024呎 (2房)
 $3038万
 $29,671/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7679,7 +7679,7 @@
           <t>A | 1735呎 (4+房)
 $4945万
 $28,500/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -7695,7 +7695,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,070/呎
-(16年-03月)</t>
+(16年-03月-17日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -7703,7 +7703,7 @@
           <t>D | 1702呎 (4+房)
 $3642万
 $21,400/呎
-(16年-06月)</t>
+(16年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
           <t>C | 1129呎 (3房)
 $3048万
 $27,000/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -7742,7 +7742,7 @@
           <t>D | 1639呎 (4+房)
 $4105万
 $25,047/呎
-(16年-02月)</t>
+(16年-02月-21日)</t>
         </is>
       </c>
     </row>
